--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260901.xlsx
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,891,663,036</t>
+          <t>11,407,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>11,407,000</t>
+          <t>3,891,663,036</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>10,241,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>10,241,000</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>16,642,000</t>
+          <t>9,303,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>9,303,000</t>
+          <t>16,642,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,586,000</t>
+          <t>52,656,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>52,656,000</t>
+          <t>1,586,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
